--- a/frontend/test_data/header_detection/Tricky_Dense_Top_Test.xlsx
+++ b/frontend/test_data/header_detection/Tricky_Dense_Top_Test.xlsx
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:M4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -490,18 +490,27 @@
         <v>Consistent String Signal</v>
       </c>
       <c r="F1" t="str">
+        <v>Consistent Numeric Signal</v>
+      </c>
+      <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>Numeric Data Penalty</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Pivoted Series Bonus</v>
+      </c>
+      <c r="J1" t="str">
         <v>100% String Bonus</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>Unique Values Rule</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>Orphan Header Penalty</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>TOTAL SCORE</v>
       </c>
     </row>
@@ -528,13 +537,22 @@
         <v>0</v>
       </c>
       <c r="H2">
+        <v>-20</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>5</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>23</v>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -557,15 +575,24 @@
         <v>0</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>10</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>5</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>43</v>
       </c>
     </row>
@@ -580,30 +607,39 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>10</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>70</v>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/Tricky_Dense_Top_Test.xlsx
+++ b/frontend/test_data/header_detection/Tricky_Dense_Top_Test.xlsx
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -481,37 +481,40 @@
         <v>Row Preview</v>
       </c>
       <c r="C1" t="str">
-        <v>Density Bonus</v>
+        <v>Pillar 1: Density (%)</v>
       </c>
       <c r="D1" t="str">
-        <v>Data Boundary Signal</v>
+        <v>Pillar 2: Boundary (%)</v>
       </c>
       <c r="E1" t="str">
-        <v>Consistent String Signal</v>
+        <v>Pillar 3: Consistency (%)</v>
       </c>
       <c r="F1" t="str">
-        <v>Consistent Numeric Signal</v>
+        <v>Pillar 4: Traits (%)</v>
       </c>
       <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
       <c r="H1" t="str">
-        <v>Numeric Data Penalty</v>
+        <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Pivoted Series Bonus</v>
+        <v>Search Booster (Pivoted)</v>
       </c>
       <c r="J1" t="str">
-        <v>100% String Bonus</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Unique Values Rule</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="L1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL SCORE</v>
+        <v>TOTAL RAW SCORE</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
     <row r="2">
@@ -522,22 +525,22 @@
         <v>["Total Spend:","150000","Total Vendors:","45"]</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -546,13 +549,16 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>-61</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -563,16 +569,16 @@
         <v>["Report Status:","FINAL","Period:","Q3"]</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -584,16 +590,19 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>43</v>
+        <v>66</v>
+      </c>
+      <c r="N3">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -604,16 +613,16 @@
         <v>["Vendor Number","Vendor Name","Street","Zip Code"</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -625,21 +634,24 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>5</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
       <c r="M4">
-        <v>52</v>
+        <v>72</v>
+      </c>
+      <c r="N4">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/Tricky_Dense_Top_Test.xlsx
+++ b/frontend/test_data/header_detection/Tricky_Dense_Top_Test.xlsx
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:M4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -499,21 +499,18 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
@@ -549,15 +546,12 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>-61</v>
       </c>
       <c r="M2">
-        <v>-61</v>
-      </c>
-      <c r="N2">
         <v>0</v>
       </c>
     </row>
@@ -593,15 +587,12 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="M3">
-        <v>66</v>
-      </c>
-      <c r="N3">
         <v>66</v>
       </c>
     </row>
@@ -637,21 +628,18 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="M4">
         <v>72</v>
       </c>
-      <c r="N4">
-        <v>72</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>